--- a/Result/profitability/3005.xlsx
+++ b/Result/profitability/3005.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.78125</v>
+        <v>1.865</v>
       </c>
       <c r="N2" t="n">
-        <v>29.72875</v>
+        <v>29.685</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>1.59375</v>
+        <v>1.69375</v>
       </c>
       <c r="N3" t="n">
-        <v>27.655</v>
+        <v>27.64</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1.46625</v>
+        <v>1.53375</v>
       </c>
       <c r="N4" t="n">
-        <v>26.0225</v>
+        <v>26.09625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3075</v>
+        <v>1.34</v>
       </c>
       <c r="N5" t="n">
-        <v>24.3475</v>
+        <v>24.11125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07625</v>
+        <v>1.12625</v>
       </c>
       <c r="N6" t="n">
-        <v>22.24</v>
+        <v>22.25875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8875</v>
+        <v>0.94375</v>
       </c>
       <c r="N7" t="n">
-        <v>20.84</v>
+        <v>20.92375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.78</v>
       </c>
       <c r="M8" t="n">
-        <v>0.72625</v>
+        <v>0.82375</v>
       </c>
       <c r="N8" t="n">
-        <v>19.47375</v>
+        <v>19.5525</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5862499999999999</v>
+        <v>0.58625</v>
       </c>
       <c r="N10" t="n">
         <v>18.07</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11513</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7864</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3648</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1936</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>108</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2044</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1573</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.0325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4482758620689655</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6300000000000026</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02028332260141674</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2600000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1150442477876108</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.889999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05628350208457411</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
